--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbinvesttrade/ChbInvestTrade001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbinvesttrade/ChbInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\产品3.0.7单信披\tams\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\report\chb\businessdatamaintain\chbinvesttrade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\product\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\report\chb\businessdatamaintain\chbinvesttrade\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>数据状态</t>
   </si>
@@ -103,6 +103,10 @@
   </si>
   <si>
     <t>折算人民币金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行内交易编码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -207,7 +211,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -242,7 +246,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -451,30 +455,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AC1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="14.875" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="20.5" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="16" max="16" width="13.25" customWidth="1"/>
-    <col min="17" max="17" width="19.5" customWidth="1"/>
-    <col min="18" max="18" width="19.375" customWidth="1"/>
-    <col min="19" max="19" width="11.375" customWidth="1"/>
-    <col min="20" max="20" width="16.25" customWidth="1"/>
-    <col min="21" max="21" width="20.5" customWidth="1"/>
-    <col min="22" max="22" width="16.5" customWidth="1"/>
-    <col min="23" max="23" width="15.75" customWidth="1"/>
-    <col min="24" max="24" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" customWidth="1"/>
+    <col min="4" max="5" width="16.90625" customWidth="1"/>
+    <col min="6" max="6" width="20.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="17" max="17" width="13.26953125" customWidth="1"/>
+    <col min="18" max="18" width="19.453125" customWidth="1"/>
+    <col min="19" max="19" width="19.36328125" customWidth="1"/>
+    <col min="20" max="20" width="11.36328125" customWidth="1"/>
+    <col min="21" max="21" width="16.26953125" customWidth="1"/>
+    <col min="22" max="22" width="20.453125" customWidth="1"/>
+    <col min="23" max="23" width="16.453125" customWidth="1"/>
+    <col min="24" max="24" width="15.7265625" customWidth="1"/>
+    <col min="25" max="25" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,75 +492,78 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbinvesttrade/ChbInvestTrade001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/report/chb/businessdatamaintain/chbinvesttrade/ChbInvestTrade001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\guilin\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\report\chb\businessdatamaintain\chbinvesttrade\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9300"/>
+    <workbookView windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>数据状态</t>
   </si>
@@ -33,6 +28,9 @@
     <t>发行机构代码</t>
   </si>
   <si>
+    <t>行内交易编码</t>
+  </si>
+  <si>
     <t>行内资产/负债编码</t>
   </si>
   <si>
@@ -45,7 +43,7 @@
     <t>发生金额</t>
   </si>
   <si>
-    <t>这算人民币金额</t>
+    <t>折算人民币金额</t>
   </si>
   <si>
     <t>数量</t>
@@ -63,9 +61,15 @@
     <t>交易日</t>
   </si>
   <si>
+    <t>交易发起时间</t>
+  </si>
+  <si>
     <t>交易对手</t>
   </si>
   <si>
+    <t>关联交易情况</t>
+  </si>
+  <si>
     <t>交易对手类型</t>
   </si>
   <si>
@@ -103,21 +107,19 @@
   </si>
   <si>
     <t>更新人</t>
-  </si>
-  <si>
-    <t>关联交易情况</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易发起时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,21 +128,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -148,24 +474,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -452,36 +1064,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AE1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="1"/>
-    <col min="2" max="2" width="14.90625" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" customWidth="1"/>
-    <col min="4" max="4" width="16.90625" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" customWidth="1"/>
-    <col min="11" max="11" width="12.81640625" customWidth="1"/>
-    <col min="12" max="12" width="13.54296875" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="16" max="18" width="13.1796875" customWidth="1"/>
-    <col min="19" max="19" width="19.453125" customWidth="1"/>
-    <col min="20" max="20" width="19.36328125" customWidth="1"/>
-    <col min="21" max="21" width="11.36328125" customWidth="1"/>
-    <col min="22" max="22" width="16.1796875" customWidth="1"/>
-    <col min="23" max="23" width="20.453125" customWidth="1"/>
-    <col min="24" max="24" width="16.54296875" customWidth="1"/>
-    <col min="25" max="25" width="15.81640625" customWidth="1"/>
-    <col min="26" max="26" width="11.6328125" customWidth="1"/>
+    <col min="1" max="1" width="13.0909090909091" customWidth="1"/>
+    <col min="2" max="2" width="14.9090909090909" customWidth="1"/>
+    <col min="3" max="3" width="20.0909090909091" customWidth="1"/>
+    <col min="4" max="5" width="16.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="20.4545454545455" customWidth="1"/>
+    <col min="10" max="10" width="15.3636363636364" customWidth="1"/>
+    <col min="12" max="12" width="12.8181818181818" customWidth="1"/>
+    <col min="13" max="13" width="13.5454545454545" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="13.1818181818182" customWidth="1"/>
+    <col min="17" max="17" width="13.9090909090909" customWidth="1"/>
+    <col min="18" max="18" width="13.1818181818182" customWidth="1"/>
+    <col min="19" max="19" width="18.3636363636364" customWidth="1"/>
+    <col min="20" max="20" width="19.4545454545455" customWidth="1"/>
+    <col min="21" max="21" width="19.3636363636364" customWidth="1"/>
+    <col min="22" max="22" width="11.3636363636364" customWidth="1"/>
+    <col min="23" max="23" width="16.1818181818182" customWidth="1"/>
+    <col min="24" max="24" width="20.4545454545455" customWidth="1"/>
+    <col min="25" max="25" width="16.5454545454545" customWidth="1"/>
+    <col min="26" max="26" width="15.8181818181818" customWidth="1"/>
+    <col min="27" max="27" width="11.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,51 +1147,54 @@
         <v>15</v>
       </c>
       <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="S1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>27</v>
+      <c r="AE1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>